--- a/Attendance_2026_10_27.xlsx
+++ b/Attendance_2026_10_27.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Attendance 2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ &quot;ل.س.‏&quot;_-;\-* #,##0.00\ &quot;ل.س.‏&quot;_-;_-* &quot;-&quot;??\ &quot;ل.س.‏&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,92 +29,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="2"/>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="178"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="16"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Segoe UI"/>
-      <color rgb="00000000"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -123,8 +45,14 @@
       <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -133,30 +61,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDF5"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,166 +100,107 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="00E5E7EB"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="00E5E7EB"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="00E5E7EB"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 4" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 3" xfId="3"/>
-    <cellStyle name="Normal 3" xfId="4"/>
-    <cellStyle name="Normal 2 2" xfId="5"/>
-    <cellStyle name="Normal 5" xfId="6"/>
-    <cellStyle name="Currency 2" xfId="7"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -408,44 +283,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -472,15 +347,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -507,7 +381,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -519,142 +392,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -664,19 +561,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="9" min="4" max="5"/>
-    <col width="9.140625" customWidth="1" style="9" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" style="10" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -717,7 +617,7 @@
           <t>UserName (AR)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -729,430 +629,418 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Omar Elnemr</t>
         </is>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="4" t="n">
         <v>46322</v>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>عمر النمر</t>
         </is>
       </c>
-      <c r="I2" s="28" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>OFF (Rest Day)</t>
         </is>
       </c>
-      <c r="J2" s="29" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Mohammad Almohammad</t>
         </is>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C3" s="11" t="n">
         <v>46322</v>
       </c>
-      <c r="D3" s="30" t="n">
+      <c r="D3" s="12" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="E3" s="30" t="n">
+      <c r="E3" s="12" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>محمد المحمد</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="J3" s="29" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Hanan Tinawi</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="17" t="n">
         <v>46322</v>
       </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="15" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>حنان تيناوي</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>⏳ Awaiting Report</t>
         </is>
       </c>
-      <c r="J4" s="29" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Osama Alkabbani</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="11" t="n">
         <v>46322</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="12" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="12" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>اسامة القباني</t>
         </is>
       </c>
-      <c r="I5" s="31" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Yasmin Tatary</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="23" t="n">
         <v>46322</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="24" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="24" t="n">
         <v>0.65625</v>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>ياسمين ططري</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Joudi Alghorani</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="11" t="n">
         <v>46322</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.65625</v>
       </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>جودي الغوراني</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Khaled Mohammad Mlas</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="17" t="n">
         <v>46322</v>
       </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>محمد خالد ملص</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>⏳ Awaiting Report</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Raboushee</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="17" t="n">
         <v>46322</v>
       </c>
-      <c r="D9" s="30" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ربى </t>
-        </is>
-      </c>
-      <c r="I9" s="31" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>ربى</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>⏳ Awaiting Report</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Rasheed Akel</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="23" t="n">
         <v>46322</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="24" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="24" t="n">
         <v>0.7958333333333333</v>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>رشيد عاقل</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="J10" s="34" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="14" t="n"/>
-      <c r="J13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="14" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J10:J14">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Attendance_2026_10_27.xlsx
+++ b/Attendance_2026_10_27.xlsx
@@ -901,48 +901,48 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Khaled Mohammad Mlas</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="4" t="n">
         <v>46322</v>
       </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>محمد خالد ملص</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>⏳ Awaiting Report</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>OFF (Rest Day)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>

--- a/Attendance_2026_10_27.xlsx
+++ b/Attendance_2026_10_27.xlsx
@@ -721,48 +721,48 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Hanan Tinawi</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="4" t="n">
         <v>46322</v>
       </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>حنان تيناوي</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
-        <is>
-          <t>⏳ Awaiting Report</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>OFF (Rest Day)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>FlyDubi</t>
         </is>
